--- a/Regionalized FeliX/Model Files/TotalPopulationbyAge.xlsx
+++ b/Regionalized FeliX/Model Files/TotalPopulationbyAge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iiasahub-my.sharepoint.com/personal/yequanliang_iiasa_ac_at/Documents/research_iiasa/Felix-Model/Regionalied FeliX/Model Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iiasahub-my.sharepoint.com/personal/yequanliang_iiasa_ac_at/Documents/research_iiasa/Felix-Model/Regionalized FeliX/Model Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3770" documentId="13_ncr:1_{FE6EE77C-DE09-4F18-A09F-03FA1D28A0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C546F660-7C89-4520-B6A5-A56D86690FA7}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1080" yWindow="1080" windowWidth="17280" windowHeight="8880" tabRatio="759" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2820" yWindow="2820" windowWidth="17280" windowHeight="8880" tabRatio="759" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
